--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_h_8.xlsx
@@ -658,7 +658,7 @@
         <v>0.008444969144207771</v>
       </c>
       <c r="C2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>35688951</v>
+        <v>4036644</v>
       </c>
       <c r="L2" t="n">
-        <v>19904213</v>
+        <v>1970940</v>
       </c>
       <c r="M2" t="n">
-        <v>4651051</v>
+        <v>421499</v>
       </c>
       <c r="N2" t="n">
-        <v>194870</v>
+        <v>13452</v>
       </c>
       <c r="O2" t="n">
-        <v>2712800</v>
+        <v>249908</v>
       </c>
       <c r="P2" t="n">
-        <v>1096897</v>
+        <v>107168</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998980164527893</v>
+        <v>0.9999027252197266</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8714180588722229</v>
+        <v>0.7829599380493164</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7519317269325256</v>
+        <v>0.599278450012207</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6898658871650696</v>
+        <v>0.4971943497657776</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2043461501598358</v>
+        <v>0.1112977266311646</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7379682064056396</v>
+        <v>0.5633646845817566</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8244884610176086</v>
+        <v>0.6726841330528259</v>
       </c>
       <c r="X2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>38435590</v>
+        <v>4776143</v>
       </c>
       <c r="AG2" t="n">
-        <v>23824653</v>
+        <v>2997819</v>
       </c>
       <c r="AH2" t="n">
-        <v>6405435</v>
+        <v>803798</v>
       </c>
       <c r="AI2" t="n">
-        <v>472232</v>
+        <v>59153</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3675525</v>
+        <v>460411</v>
       </c>
       <c r="AK2" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9562234282493591</v>
+        <v>0.9553927183151245</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114547371864319</v>
+        <v>0.9118788242340088</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582150936126709</v>
+        <v>0.85825514793396</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6619678735733032</v>
+        <v>0.661193311214447</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020171165466309</v>
+        <v>0.9019849300384521</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314440488815308</v>
+        <v>0.9314650297164917</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002024809124862332</v>
       </c>
       <c r="C3" t="n">
-        <v>1635</v>
+        <v>214</v>
       </c>
       <c r="D3" t="n">
-        <v>35688951</v>
+        <v>4036644</v>
       </c>
       <c r="E3" t="n">
-        <v>4333768</v>
+        <v>911425</v>
       </c>
       <c r="F3" t="n">
-        <v>99534</v>
+        <v>34805</v>
       </c>
       <c r="G3" t="n">
-        <v>9751</v>
+        <v>2944</v>
       </c>
       <c r="H3" t="n">
-        <v>5952</v>
+        <v>2459</v>
       </c>
       <c r="I3" t="n">
-        <v>382</v>
+        <v>193</v>
       </c>
       <c r="J3" t="n">
-        <v>80127826</v>
+        <v>10016008</v>
       </c>
       <c r="K3" t="n">
-        <v>85230750</v>
+        <v>10221940</v>
       </c>
       <c r="L3" t="n">
-        <v>97886378</v>
+        <v>11715774</v>
       </c>
       <c r="M3" t="n">
-        <v>121075069</v>
+        <v>14965404</v>
       </c>
       <c r="N3" t="n">
-        <v>129163984</v>
+        <v>16132583</v>
       </c>
       <c r="O3" t="n">
-        <v>125596421</v>
+        <v>15625016</v>
       </c>
       <c r="P3" t="n">
-        <v>128856178</v>
+        <v>16083864</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8891124725341797</v>
+        <v>0.8091601133346558</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7601709365844727</v>
+        <v>0.5979955196380615</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6225624680519104</v>
+        <v>0.4493880271911621</v>
       </c>
       <c r="U3" t="n">
-        <v>0.272904634475708</v>
+        <v>0.1501272320747375</v>
       </c>
       <c r="V3" t="n">
-        <v>0.665368378162384</v>
+        <v>0.4891591668128967</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7089919447898865</v>
+        <v>0.5535823106765747</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>38435590</v>
+        <v>4776143</v>
       </c>
       <c r="Z3" t="n">
-        <v>1581425</v>
+        <v>197221</v>
       </c>
       <c r="AA3" t="n">
-        <v>68001</v>
+        <v>8441</v>
       </c>
       <c r="AB3" t="n">
-        <v>54459</v>
+        <v>6838</v>
       </c>
       <c r="AC3" t="n">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>80132976</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>88737218</v>
+        <v>11117918</v>
       </c>
       <c r="AG3" t="n">
-        <v>102138438</v>
+        <v>12743989</v>
       </c>
       <c r="AH3" t="n">
-        <v>122107746</v>
+        <v>15258909</v>
       </c>
       <c r="AI3" t="n">
-        <v>129681597</v>
+        <v>16209685</v>
       </c>
       <c r="AJ3" t="n">
-        <v>126160401</v>
+        <v>15768676</v>
       </c>
       <c r="AK3" t="n">
-        <v>128983636</v>
+        <v>16122748</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575390219688416</v>
+        <v>0.9573953747749329</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098982810974121</v>
+        <v>0.909557044506073</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573940396308899</v>
+        <v>0.8569823503494263</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6613346934318542</v>
+        <v>0.6601602435112</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014958739280701</v>
+        <v>0.9011887311935425</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312471747398376</v>
+        <v>0.9310656785964966</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0319507024117701</v>
       </c>
       <c r="C4" t="n">
-        <v>196</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
-        <v>4927626</v>
+        <v>1036444</v>
       </c>
       <c r="E4" t="n">
-        <v>19904213</v>
+        <v>1970940</v>
       </c>
       <c r="F4" t="n">
-        <v>1175926</v>
+        <v>235629</v>
       </c>
       <c r="G4" t="n">
-        <v>65848</v>
+        <v>17527</v>
       </c>
       <c r="H4" t="n">
-        <v>99331</v>
+        <v>31252</v>
       </c>
       <c r="I4" t="n">
-        <v>10724</v>
+        <v>4071</v>
       </c>
       <c r="J4" t="n">
-        <v>5150</v>
+        <v>614</v>
       </c>
       <c r="K4" t="n">
-        <v>5266077</v>
+        <v>1118976</v>
       </c>
       <c r="L4" t="n">
-        <v>6566558</v>
+        <v>1317915</v>
       </c>
       <c r="M4" t="n">
-        <v>2090913</v>
+        <v>426256</v>
       </c>
       <c r="N4" t="n">
-        <v>758757</v>
+        <v>107413</v>
       </c>
       <c r="O4" t="n">
-        <v>963239</v>
+        <v>193691</v>
       </c>
       <c r="P4" t="n">
-        <v>233500</v>
+        <v>52146</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999949038028717</v>
+        <v>0.9999513626098633</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8801763653755188</v>
+        <v>0.7958444952964783</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7560288906097412</v>
+        <v>0.5986363291740417</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6544884443283081</v>
+        <v>0.4720839560031891</v>
       </c>
       <c r="U4" t="n">
-        <v>0.233701080083847</v>
+        <v>0.1278287917375565</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6997904181480408</v>
+        <v>0.5236461162567139</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7623907923698425</v>
+        <v>0.6073493361473083</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1643061</v>
+        <v>208344</v>
       </c>
       <c r="Z4" t="n">
-        <v>23824653</v>
+        <v>2997819</v>
       </c>
       <c r="AA4" t="n">
-        <v>662423</v>
+        <v>82986</v>
       </c>
       <c r="AB4" t="n">
-        <v>44064</v>
+        <v>5563</v>
       </c>
       <c r="AC4" t="n">
-        <v>9119</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1759609</v>
+        <v>222998</v>
       </c>
       <c r="AG4" t="n">
-        <v>2314498</v>
+        <v>289700</v>
       </c>
       <c r="AH4" t="n">
-        <v>1058236</v>
+        <v>132751</v>
       </c>
       <c r="AI4" t="n">
-        <v>241144</v>
+        <v>30311</v>
       </c>
       <c r="AJ4" t="n">
-        <v>399259</v>
+        <v>50031</v>
       </c>
       <c r="AK4" t="n">
-        <v>106042</v>
+        <v>13262</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568807482719421</v>
+        <v>0.9563930034637451</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106758832931519</v>
+        <v>0.9107164144515991</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578044176101685</v>
+        <v>0.8576182723045349</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6616511344909668</v>
+        <v>0.6606763601303101</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017564058303833</v>
+        <v>0.901586651802063</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313456416130066</v>
+        <v>0.9312652945518494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1540</v>
+        <v>205</v>
       </c>
       <c r="D5" t="n">
-        <v>229145</v>
+        <v>60070</v>
       </c>
       <c r="E5" t="n">
-        <v>1874533</v>
+        <v>322856</v>
       </c>
       <c r="F5" t="n">
-        <v>4651051</v>
+        <v>421499</v>
       </c>
       <c r="G5" t="n">
-        <v>263943</v>
+        <v>35123</v>
       </c>
       <c r="H5" t="n">
-        <v>406989</v>
+        <v>85411</v>
       </c>
       <c r="I5" t="n">
-        <v>43617</v>
+        <v>12776</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4451022</v>
+        <v>952040</v>
       </c>
       <c r="L5" t="n">
-        <v>6279651</v>
+        <v>1324971</v>
       </c>
       <c r="M5" t="n">
-        <v>2819767</v>
+        <v>516441</v>
       </c>
       <c r="N5" t="n">
-        <v>519189</v>
+        <v>76152</v>
       </c>
       <c r="O5" t="n">
-        <v>1364340</v>
+        <v>260985</v>
       </c>
       <c r="P5" t="n">
-        <v>450225</v>
+        <v>86422</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999606013298035</v>
+        <v>0.9999623894691467</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9256174564361572</v>
+        <v>0.8731741309165955</v>
       </c>
       <c r="S5" t="n">
-        <v>0.901664674282074</v>
+        <v>0.8381536602973938</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9624096751213074</v>
+        <v>0.9422706365585327</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9902175664901733</v>
+        <v>0.9887587428092957</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9821828007698059</v>
+        <v>0.9721563458442688</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9947662353515625</v>
+        <v>0.9915143251419067</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>64236</v>
+        <v>8050</v>
       </c>
       <c r="Z5" t="n">
-        <v>683114</v>
+        <v>86223</v>
       </c>
       <c r="AA5" t="n">
-        <v>6405435</v>
+        <v>803798</v>
       </c>
       <c r="AB5" t="n">
-        <v>79701</v>
+        <v>9997</v>
       </c>
       <c r="AC5" t="n">
-        <v>233268</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>5064</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1704383</v>
+        <v>212541</v>
       </c>
       <c r="AG5" t="n">
-        <v>2359211</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>1065383</v>
+        <v>134142</v>
       </c>
       <c r="AI5" t="n">
-        <v>241827</v>
+        <v>30451</v>
       </c>
       <c r="AJ5" t="n">
-        <v>401615</v>
+        <v>50482</v>
       </c>
       <c r="AK5" t="n">
-        <v>106369</v>
+        <v>13345</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734838008880615</v>
+        <v>0.9733282327651978</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642236232757568</v>
+        <v>0.9640045166015625</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837440848350525</v>
+        <v>0.9836558699607849</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963029623031616</v>
+        <v>0.9962790012359619</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938694834709167</v>
+        <v>0.993844747543335</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983740448951721</v>
+        <v>0.9983706474304199</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>278</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>98923</v>
+        <v>17106</v>
       </c>
       <c r="E6" t="n">
-        <v>166484</v>
+        <v>23328</v>
       </c>
       <c r="F6" t="n">
-        <v>173298</v>
+        <v>23695</v>
       </c>
       <c r="G6" t="n">
-        <v>194870</v>
+        <v>13452</v>
       </c>
       <c r="H6" t="n">
-        <v>73547</v>
+        <v>10384</v>
       </c>
       <c r="I6" t="n">
-        <v>6659</v>
+        <v>1609</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>51905</v>
+        <v>6568</v>
       </c>
       <c r="Z6" t="n">
-        <v>42831</v>
+        <v>5365</v>
       </c>
       <c r="AA6" t="n">
-        <v>87352</v>
+        <v>11023</v>
       </c>
       <c r="AB6" t="n">
-        <v>472232</v>
+        <v>59153</v>
       </c>
       <c r="AC6" t="n">
-        <v>55891</v>
+        <v>7014</v>
       </c>
       <c r="AD6" t="n">
-        <v>3848</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>309</v>
+        <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>9993</v>
+        <v>5247</v>
       </c>
       <c r="E7" t="n">
-        <v>178196</v>
+        <v>54943</v>
       </c>
       <c r="F7" t="n">
-        <v>607185</v>
+        <v>121086</v>
       </c>
       <c r="G7" t="n">
-        <v>396539</v>
+        <v>46181</v>
       </c>
       <c r="H7" t="n">
-        <v>2712800</v>
+        <v>249908</v>
       </c>
       <c r="I7" t="n">
-        <v>172118</v>
+        <v>33497</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>6480</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>237812</v>
+        <v>29968</v>
       </c>
       <c r="AB7" t="n">
-        <v>60794</v>
+        <v>7646</v>
       </c>
       <c r="AC7" t="n">
-        <v>3675525</v>
+        <v>460411</v>
       </c>
       <c r="AD7" t="n">
-        <v>96346</v>
+        <v>12050</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1192</v>
+        <v>86</v>
       </c>
       <c r="D8" t="n">
-        <v>390</v>
+        <v>109</v>
       </c>
       <c r="E8" t="n">
-        <v>13577</v>
+        <v>5363</v>
       </c>
       <c r="F8" t="n">
-        <v>34970</v>
+        <v>11041</v>
       </c>
       <c r="G8" t="n">
-        <v>22676</v>
+        <v>5638</v>
       </c>
       <c r="H8" t="n">
-        <v>377420</v>
+        <v>64185</v>
       </c>
       <c r="I8" t="n">
-        <v>1096897</v>
+        <v>107168</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2648</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2126</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>100723</v>
+        <v>12636</v>
       </c>
       <c r="AD8" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
